--- a/artfynd/A 37547-2023 artfynd.xlsx
+++ b/artfynd/A 37547-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 37547-2023 artfynd.xlsx
+++ b/artfynd/A 37547-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112647116</v>
+        <v>112647119</v>
       </c>
       <c r="B2" t="n">
-        <v>91075</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5448</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>714064</v>
+        <v>714075</v>
       </c>
       <c r="R2" t="n">
-        <v>7082987</v>
+        <v>7082989</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112647119</v>
+        <v>112647117</v>
       </c>
       <c r="B3" t="n">
-        <v>91024</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>714075</v>
+        <v>714069</v>
       </c>
       <c r="R3" t="n">
-        <v>7082989</v>
+        <v>7082980</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112647117</v>
+        <v>112647116</v>
       </c>
       <c r="B4" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>5448</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>714069</v>
+        <v>714064</v>
       </c>
       <c r="R4" t="n">
-        <v>7082980</v>
+        <v>7082987</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112647120</v>
+        <v>112647122</v>
       </c>
       <c r="B5" t="n">
-        <v>89300</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5741</v>
+        <v>5448</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>714082</v>
+        <v>714092</v>
       </c>
       <c r="R5" t="n">
-        <v>7082992</v>
+        <v>7083010</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112647113</v>
+        <v>112647120</v>
       </c>
       <c r="B6" t="n">
-        <v>77856</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91409</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5741</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>713961</v>
+        <v>714082</v>
       </c>
       <c r="R6" t="n">
-        <v>7082885</v>
+        <v>7082992</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112647112</v>
+        <v>112647113</v>
       </c>
       <c r="B7" t="n">
-        <v>5182</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>713918</v>
+        <v>713961</v>
       </c>
       <c r="R7" t="n">
-        <v>7082890</v>
+        <v>7082885</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,37 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112647114</v>
+        <v>112647112</v>
       </c>
       <c r="B8" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>105930</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>713962</v>
+        <v>713918</v>
       </c>
       <c r="R8" t="n">
-        <v>7082891</v>
+        <v>7082890</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,108 +1351,6 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>112647122</v>
-      </c>
-      <c r="B9" t="n">
-        <v>91075</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>5448</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Svartvit taggsvamp</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Phellodon connatus</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Schultz) nom.prov</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Skjölgforsholmen, Ång</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>714091</v>
-      </c>
-      <c r="R9" t="n">
-        <v>7083010</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Nordmaling</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Nordmaling</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2023-09-28</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2023-09-28</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Åsa Stenman</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Åsa Stenman</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37547-2023 artfynd.xlsx
+++ b/artfynd/A 37547-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112647119</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112647117</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112647116</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112647122</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112647120</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112647113</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,8 +1386,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112647112</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>